--- a/exports/trend_1d/LTM_full_report.xlsx
+++ b/exports/trend_1d/LTM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42604</v>
+        <v>42605</v>
       </c>
       <c r="H2" t="n">
-        <v>656.05</v>
+        <v>645.95</v>
       </c>
       <c r="I2" t="n">
         <v>655.8375269999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.67</v>
+        <v>-5.15</v>
       </c>
       <c r="L2" t="n">
-        <v>3.82</v>
+        <v>5.44</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0.14</v>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O2" t="n">
         <v>0.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42667</v>
+        <v>42668</v>
       </c>
       <c r="H3" t="n">
-        <v>626.45</v>
+        <v>649.25</v>
       </c>
       <c r="I3" t="n">
         <v>636.8693166642319</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" t="n">
-        <v>3.02</v>
+        <v>-0.51</v>
       </c>
       <c r="L3" t="n">
         <v>2.92</v>
@@ -612,7 +647,7 @@
         <v>0.48</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>3.64</v>
       </c>
       <c r="O3" t="n">
         <v>-1.54</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.56</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H4" t="n">
-        <v>620.15</v>
+        <v>603.65</v>
       </c>
       <c r="I4" t="n">
         <v>620.0452679129415</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.48</v>
+        <v>-7.02</v>
       </c>
       <c r="L4" t="n">
         <v>7.59</v>
@@ -669,7 +716,7 @@
         <v>4.61</v>
       </c>
       <c r="N4" t="n">
-        <v>1.77</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
         <v>3.64</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42703</v>
+        <v>42704</v>
       </c>
       <c r="H5" t="n">
-        <v>631.9</v>
+        <v>643.8</v>
       </c>
       <c r="I5" t="n">
         <v>639.987452208188</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.68</v>
+        <v>-6.65</v>
       </c>
       <c r="L5" t="n">
-        <v>5.19</v>
+        <v>7.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
         <v>2.46</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.62</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H6" t="n">
-        <v>763.4</v>
+        <v>746.35</v>
       </c>
       <c r="I6" t="n">
         <v>760.4371309171077</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K6" t="n">
-        <v>18.58</v>
+        <v>15.93</v>
       </c>
       <c r="L6" t="n">
         <v>2.14</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>8.74</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43007</v>
+        <v>43011</v>
       </c>
       <c r="H7" t="n">
-        <v>798.95</v>
+        <v>812.35</v>
       </c>
       <c r="I7" t="n">
         <v>802.7258519294188</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.05</v>
+        <v>-8.84</v>
       </c>
       <c r="L7" t="n">
-        <v>8.19</v>
+        <v>10.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.84</v>
+        <v>1.38</v>
       </c>
       <c r="N7" t="n">
         <v>4.58</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.14</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43314</v>
+        <v>43315</v>
       </c>
       <c r="H8" t="n">
-        <v>1749.85</v>
+        <v>1684.05</v>
       </c>
       <c r="I8" t="n">
         <v>1697.845770354204</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K8" t="n">
-        <v>115.41</v>
+        <v>107.31</v>
       </c>
       <c r="L8" t="n">
         <v>3.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>209</v>
+        <v>210</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.27</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43332</v>
+        <v>43333</v>
       </c>
       <c r="H9" t="n">
-        <v>1880.75</v>
+        <v>1899.5</v>
       </c>
       <c r="I9" t="n">
         <v>1890.510932731124</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.68</v>
+        <v>-12.79</v>
       </c>
       <c r="L9" t="n">
-        <v>13.12</v>
+        <v>13.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.43</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43383</v>
+        <v>43384</v>
       </c>
       <c r="H10" t="n">
-        <v>1794.85</v>
+        <v>1715.05</v>
       </c>
       <c r="I10" t="n">
         <v>1725.30612714145</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.51</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>13.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>16.58</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43446</v>
+        <v>43447</v>
       </c>
       <c r="H11" t="n">
-        <v>1623.6</v>
+        <v>1748.5</v>
       </c>
       <c r="I11" t="n">
         <v>1631.444415344619</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K11" t="n">
-        <v>5.33</v>
+        <v>-1.95</v>
       </c>
       <c r="L11" t="n">
         <v>8.98</v>
@@ -1068,7 +1199,7 @@
         <v>3.83</v>
       </c>
       <c r="N11" t="n">
-        <v>6.36</v>
+        <v>7.69</v>
       </c>
       <c r="O11" t="n">
         <v>-4.45</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>15.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43517</v>
+        <v>43518</v>
       </c>
       <c r="H12" t="n">
-        <v>1725.55</v>
+        <v>1715.15</v>
       </c>
       <c r="I12" t="n">
         <v>1719.079337436245</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.31</v>
+        <v>-1.91</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.58</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43599</v>
+        <v>43600</v>
       </c>
       <c r="H13" t="n">
-        <v>1717.4</v>
+        <v>1758.1</v>
       </c>
       <c r="I13" t="n">
         <v>1734.772457277685</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.13</v>
+        <v>-2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
         <v>1.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.79</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43649</v>
+        <v>43650</v>
       </c>
       <c r="H14" t="n">
-        <v>1735.2</v>
+        <v>1655.8</v>
       </c>
       <c r="I14" t="n">
         <v>1687.640503437017</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3</v>
+        <v>-5.82</v>
       </c>
       <c r="L14" t="n">
-        <v>4.72</v>
+        <v>6.15</v>
       </c>
       <c r="M14" t="n">
-        <v>0.54</v>
+        <v>1.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.16</v>
+        <v>4.58</v>
       </c>
       <c r="O14" t="n">
         <v>2.37</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.21</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H15" t="n">
-        <v>1610.8</v>
+        <v>1643.55</v>
       </c>
       <c r="I15" t="n">
         <v>1640.934631828797</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" t="n">
-        <v>2.72</v>
+        <v>0.74</v>
       </c>
       <c r="L15" t="n">
         <v>3.76</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43726</v>
+        <v>43727</v>
       </c>
       <c r="H16" t="n">
-        <v>1585.7</v>
+        <v>1557.1</v>
       </c>
       <c r="I16" t="n">
         <v>1559.513819065608</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.52</v>
+        <v>-5.26</v>
       </c>
       <c r="L16" t="n">
-        <v>3.93</v>
+        <v>5.62</v>
       </c>
       <c r="M16" t="n">
         <v>0.41</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.16</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H17" t="n">
-        <v>1499.15</v>
+        <v>1610.6</v>
       </c>
       <c r="I17" t="n">
         <v>1583.407886728458</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>3.72</v>
+        <v>-3.44</v>
       </c>
       <c r="L17" t="n">
-        <v>2.56</v>
+        <v>4.94</v>
       </c>
       <c r="M17" t="n">
-        <v>1.35</v>
+        <v>2.39</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>7.43</v>
       </c>
       <c r="O17" t="n">
         <v>-1.8</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.06</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43894</v>
+        <v>43895</v>
       </c>
       <c r="H18" t="n">
-        <v>1897.65</v>
+        <v>1892.2</v>
       </c>
       <c r="I18" t="n">
         <v>1893.589028458921</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K18" t="n">
-        <v>17.82</v>
+        <v>17.48</v>
       </c>
       <c r="L18" t="n">
         <v>4.69</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.77</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43970</v>
+        <v>43971</v>
       </c>
       <c r="H19" t="n">
-        <v>1670.15</v>
+        <v>1784</v>
       </c>
       <c r="I19" t="n">
         <v>1677.641542745977</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K19" t="n">
-        <v>11.74</v>
+        <v>5.72</v>
       </c>
       <c r="L19" t="n">
         <v>2.26</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.71</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44096</v>
+        <v>44097</v>
       </c>
       <c r="H20" t="n">
-        <v>2579.85</v>
+        <v>2448.45</v>
       </c>
       <c r="I20" t="n">
         <v>2471.75691323667</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K20" t="n">
-        <v>44.61</v>
+        <v>37.24</v>
       </c>
       <c r="L20" t="n">
         <v>4.09</v>
@@ -1581,7 +1820,7 @@
         <v>2.83</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>5.09</v>
       </c>
       <c r="O20" t="n">
         <v>6.82</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>18.54</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H21" t="n">
-        <v>2667.1</v>
+        <v>2861.4</v>
       </c>
       <c r="I21" t="n">
         <v>2800.617831725421</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.93</v>
+        <v>-16.87</v>
       </c>
       <c r="L21" t="n">
-        <v>11.01</v>
+        <v>20.85</v>
       </c>
       <c r="M21" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="N21" t="n">
-        <v>3.88</v>
+        <v>7.29</v>
       </c>
       <c r="O21" t="n">
         <v>-5.09</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>13.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44243</v>
+        <v>44244</v>
       </c>
       <c r="H22" t="n">
-        <v>3944.95</v>
+        <v>3875.9</v>
       </c>
       <c r="I22" t="n">
         <v>3885.269945039876</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K22" t="n">
-        <v>37.87</v>
+        <v>35.45</v>
       </c>
       <c r="L22" t="n">
         <v>5.01</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>12.01</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44264</v>
+        <v>44265</v>
       </c>
       <c r="H23" t="n">
-        <v>3896.5</v>
+        <v>4128.95</v>
       </c>
       <c r="I23" t="n">
         <v>3981.049525953329</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.53</v>
+        <v>-6.53</v>
       </c>
       <c r="L23" t="n">
-        <v>3.59</v>
+        <v>7.07</v>
       </c>
       <c r="M23" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="N23" t="n">
         <v>6.23</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.41</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44314</v>
+        <v>44315</v>
       </c>
       <c r="H24" t="n">
-        <v>3890.85</v>
+        <v>3851</v>
       </c>
       <c r="I24" t="n">
         <v>3889.482815932784</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.77</v>
+        <v>-6.73</v>
       </c>
       <c r="L24" t="n">
         <v>8.33</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="H25" t="n">
-        <v>3799.85</v>
+        <v>3924.3</v>
       </c>
       <c r="I25" t="n">
         <v>3909.85665814627</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>1.33</v>
+        <v>-1.9</v>
       </c>
       <c r="L25" t="n">
         <v>2.96</v>
@@ -1866,7 +2165,7 @@
         <v>1.48</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="O25" t="n">
         <v>-1.02</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44474</v>
+        <v>44475</v>
       </c>
       <c r="H26" t="n">
-        <v>5765.4</v>
+        <v>5688.85</v>
       </c>
       <c r="I26" t="n">
         <v>5694.243588956357</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K26" t="n">
-        <v>46.92</v>
+        <v>44.96</v>
       </c>
       <c r="L26" t="n">
         <v>3.93</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.49</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44487</v>
+        <v>44488</v>
       </c>
       <c r="H27" t="n">
-        <v>5905.85</v>
+        <v>6855.15</v>
       </c>
       <c r="I27" t="n">
         <v>6342.75365842707</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.81</v>
+        <v>-20.5</v>
       </c>
       <c r="L27" t="n">
-        <v>10.27</v>
+        <v>24.16</v>
       </c>
       <c r="M27" t="n">
-        <v>1.83</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>3.56</v>
+        <v>16.07</v>
       </c>
       <c r="O27" t="n">
         <v>-1.33</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.47</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H28" t="n">
-        <v>6849.8</v>
+        <v>6648.3</v>
       </c>
       <c r="I28" t="n">
         <v>6712.670533573375</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.08</v>
+        <v>-3.02</v>
       </c>
       <c r="L28" t="n">
         <v>8.619999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.83</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44557</v>
+        <v>44558</v>
       </c>
       <c r="H29" t="n">
-        <v>7181.25</v>
+        <v>7271.95</v>
       </c>
       <c r="I29" t="n">
         <v>7194.180504417961</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.02</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>8.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>1.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.92</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44578</v>
+        <v>44579</v>
       </c>
       <c r="H30" t="n">
-        <v>7103</v>
+        <v>6869.5</v>
       </c>
       <c r="I30" t="n">
         <v>6961.359395892926</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.32</v>
+        <v>-5.53</v>
       </c>
       <c r="L30" t="n">
-        <v>4.07</v>
+        <v>5.8</v>
       </c>
       <c r="M30" t="n">
         <v>0.92</v>
       </c>
       <c r="N30" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
         <v>1.26</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.9</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44627</v>
+        <v>44628</v>
       </c>
       <c r="H31" t="n">
-        <v>6212.75</v>
+        <v>6437.75</v>
       </c>
       <c r="I31" t="n">
         <v>6374.40031268758</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K31" t="n">
-        <v>9.56</v>
+        <v>6.29</v>
       </c>
       <c r="L31" t="n">
         <v>4.21</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>13.34</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H32" t="n">
-        <v>5873.65</v>
+        <v>5472.35</v>
       </c>
       <c r="I32" t="n">
         <v>5804.084129483654</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.76</v>
+        <v>-15</v>
       </c>
       <c r="L32" t="n">
-        <v>9.890000000000001</v>
+        <v>16.66</v>
       </c>
       <c r="M32" t="n">
         <v>2.28</v>
       </c>
       <c r="N32" t="n">
-        <v>3.74</v>
+        <v>6.83</v>
       </c>
       <c r="O32" t="n">
         <v>3.62</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>16.13</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H33" t="n">
-        <v>4310.95</v>
+        <v>4444.65</v>
       </c>
       <c r="I33" t="n">
         <v>4366.663428896604</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K33" t="n">
-        <v>21.22</v>
+        <v>18.78</v>
       </c>
       <c r="L33" t="n">
         <v>8.25</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>11.81</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H34" t="n">
-        <v>4658.95</v>
+        <v>4471.85</v>
       </c>
       <c r="I34" t="n">
         <v>4563.622426305541</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>4.82</v>
+        <v>0.61</v>
       </c>
       <c r="L34" t="n">
         <v>3.85</v>
       </c>
       <c r="M34" t="n">
-        <v>2.05</v>
+        <v>4.46</v>
       </c>
       <c r="N34" t="n">
         <v>4.15</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44858</v>
+        <v>44859</v>
       </c>
       <c r="H35" t="n">
-        <v>4738.3</v>
+        <v>4809.7</v>
       </c>
       <c r="I35" t="n">
         <v>4766.704495795604</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.96</v>
+        <v>-7.56</v>
       </c>
       <c r="L35" t="n">
         <v>8.460000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44883</v>
+        <v>44886</v>
       </c>
       <c r="H36" t="n">
-        <v>4895.9</v>
+        <v>4766.85</v>
       </c>
       <c r="I36" t="n">
         <v>4820.272886100699</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K36" t="n">
-        <v>1.79</v>
+        <v>-0.89</v>
       </c>
       <c r="L36" t="n">
         <v>5.29</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.72</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H37" t="n">
-        <v>4388.1</v>
+        <v>4587.75</v>
       </c>
       <c r="I37" t="n">
         <v>4520.587192203453</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K37" t="n">
-        <v>7.95</v>
+        <v>3.76</v>
       </c>
       <c r="L37" t="n">
         <v>7.51</v>
@@ -2550,7 +2993,7 @@
         <v>1.5</v>
       </c>
       <c r="N37" t="n">
-        <v>4.29</v>
+        <v>4.55</v>
       </c>
       <c r="O37" t="n">
         <v>-2.64</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.12</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H38" t="n">
-        <v>4646.4</v>
+        <v>4332.6</v>
       </c>
       <c r="I38" t="n">
         <v>4528.684856363847</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K38" t="n">
-        <v>1.28</v>
+        <v>-5.56</v>
       </c>
       <c r="L38" t="n">
-        <v>4.2</v>
+        <v>8.85</v>
       </c>
       <c r="M38" t="n">
-        <v>2.42</v>
+        <v>3.54</v>
       </c>
       <c r="N38" t="n">
-        <v>3.76</v>
+        <v>6.75</v>
       </c>
       <c r="O38" t="n">
         <v>4.55</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.61</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45044</v>
+        <v>45048</v>
       </c>
       <c r="H39" t="n">
-        <v>4419.45</v>
+        <v>4548.25</v>
       </c>
       <c r="I39" t="n">
         <v>4541.710199217846</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-2</v>
+        <v>-4.98</v>
       </c>
       <c r="L39" t="n">
-        <v>3.63</v>
+        <v>6.52</v>
       </c>
       <c r="M39" t="n">
         <v>0.7</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45117</v>
+        <v>45118</v>
       </c>
       <c r="H40" t="n">
-        <v>4997.75</v>
+        <v>4924.25</v>
       </c>
       <c r="I40" t="n">
         <v>4928.183114021818</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K40" t="n">
-        <v>9.880000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="L40" t="n">
         <v>2.73</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.75</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H41" t="n">
-        <v>5193.3</v>
+        <v>5197.9</v>
       </c>
       <c r="I41" t="n">
         <v>5193.535936359711</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.46</v>
+        <v>-5.56</v>
       </c>
       <c r="L41" t="n">
         <v>7.55</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45197</v>
+        <v>45198</v>
       </c>
       <c r="H42" t="n">
-        <v>5264.9</v>
+        <v>5209.85</v>
       </c>
       <c r="I42" t="n">
         <v>5242.174084474047</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K42" t="n">
-        <v>1.29</v>
+        <v>0.23</v>
       </c>
       <c r="L42" t="n">
         <v>3.58</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>6.54</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45217</v>
+        <v>45218</v>
       </c>
       <c r="H43" t="n">
-        <v>5155.2</v>
+        <v>5457.8</v>
       </c>
       <c r="I43" t="n">
         <v>5442.160580331062</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>1.05</v>
+        <v>-4.76</v>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>5.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="N43" t="n">
-        <v>1.32</v>
+        <v>5.87</v>
       </c>
       <c r="O43" t="n">
         <v>-1.05</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H44" t="n">
-        <v>5149.2</v>
+        <v>5060.4</v>
       </c>
       <c r="I44" t="n">
         <v>5067.067179931839</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.65</v>
+        <v>-7.28</v>
       </c>
       <c r="L44" t="n">
-        <v>7.17</v>
+        <v>7.45</v>
       </c>
       <c r="M44" t="n">
         <v>0.98</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.26</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H45" t="n">
-        <v>5401.65</v>
+        <v>5519.5</v>
       </c>
       <c r="I45" t="n">
         <v>5416.149380129358</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.74</v>
+        <v>-9.07</v>
       </c>
       <c r="L45" t="n">
-        <v>7.59</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.34</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.12</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45294</v>
+        <v>45295</v>
       </c>
       <c r="H46" t="n">
-        <v>5961.05</v>
+        <v>5866.4</v>
       </c>
       <c r="I46" t="n">
         <v>5884.933072811431</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>6.28</v>
       </c>
       <c r="L46" t="n">
         <v>2.78</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.48</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H47" t="n">
-        <v>4839.75</v>
+        <v>4892.05</v>
       </c>
       <c r="I47" t="n">
         <v>4856.603926110199</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K47" t="n">
-        <v>17.5</v>
+        <v>16.61</v>
       </c>
       <c r="L47" t="n">
         <v>9.81</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.14</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H48" t="n">
-        <v>4701.9</v>
+        <v>4649.4</v>
       </c>
       <c r="I48" t="n">
         <v>4663.335132702105</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.89</v>
+        <v>-4.96</v>
       </c>
       <c r="L48" t="n">
-        <v>4.33</v>
+        <v>5.16</v>
       </c>
       <c r="M48" t="n">
         <v>0.63</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.78</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="H49" t="n">
-        <v>4800.25</v>
+        <v>4977.2</v>
       </c>
       <c r="I49" t="n">
         <v>4894.528282240734</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.24</v>
+        <v>-7.05</v>
       </c>
       <c r="L49" t="n">
-        <v>3.78</v>
+        <v>7.71</v>
       </c>
       <c r="M49" t="n">
         <v>2.62</v>
       </c>
       <c r="N49" t="n">
-        <v>2.38</v>
+        <v>3.69</v>
       </c>
       <c r="O49" t="n">
         <v>-1.12</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.32</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45511</v>
+        <v>45512</v>
       </c>
       <c r="H50" t="n">
-        <v>5567.5</v>
+        <v>5338.3</v>
       </c>
       <c r="I50" t="n">
         <v>5384.080786912477</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K50" t="n">
-        <v>11.86</v>
+        <v>7.26</v>
       </c>
       <c r="L50" t="n">
         <v>3.16</v>
@@ -3291,7 +3890,7 @@
         <v>4.57</v>
       </c>
       <c r="N50" t="n">
-        <v>2.98</v>
+        <v>4.12</v>
       </c>
       <c r="O50" t="n">
         <v>3.69</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.77</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45531</v>
+        <v>45532</v>
       </c>
       <c r="H51" t="n">
-        <v>5751.55</v>
+        <v>6127.55</v>
       </c>
       <c r="I51" t="n">
         <v>5800.97153942992</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.74</v>
+        <v>-14.78</v>
       </c>
       <c r="L51" t="n">
-        <v>8.630000000000001</v>
+        <v>16.12</v>
       </c>
       <c r="M51" t="n">
         <v>1.91</v>
       </c>
       <c r="N51" t="n">
-        <v>2.51</v>
+        <v>6.54</v>
       </c>
       <c r="O51" t="n">
         <v>-4.12</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45582</v>
+        <v>45583</v>
       </c>
       <c r="H52" t="n">
-        <v>6394.45</v>
+        <v>5991.7</v>
       </c>
       <c r="I52" t="n">
         <v>6070.926211058802</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K52" t="n">
-        <v>4.36</v>
+        <v>-2.22</v>
       </c>
       <c r="L52" t="n">
         <v>5.84</v>
@@ -3405,7 +4028,7 @@
         <v>2.29</v>
       </c>
       <c r="N52" t="n">
-        <v>3.81</v>
+        <v>6.3</v>
       </c>
       <c r="O52" t="n">
         <v>6.54</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.65</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="H53" t="n">
-        <v>5931.05</v>
+        <v>6133.7</v>
       </c>
       <c r="I53" t="n">
         <v>6115.313989313036</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>1.01</v>
+        <v>-2.37</v>
       </c>
       <c r="L53" t="n">
         <v>6.48</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H54" t="n">
-        <v>6574.05</v>
+        <v>6220.6</v>
       </c>
       <c r="I54" t="n">
         <v>6354.282545165445</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>7.18</v>
+        <v>1.42</v>
       </c>
       <c r="L54" t="n">
         <v>3.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0.48</v>
+        <v>3.1</v>
       </c>
       <c r="N54" t="n">
-        <v>1.84</v>
+        <v>5.38</v>
       </c>
       <c r="O54" t="n">
         <v>3.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.5</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H55" t="n">
-        <v>5840.7</v>
+        <v>6124.4</v>
       </c>
       <c r="I55" t="n">
         <v>6045.426762208197</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>6.11</v>
+        <v>1.55</v>
       </c>
       <c r="L55" t="n">
         <v>2.4</v>
@@ -3576,7 +4235,7 @@
         <v>1.93</v>
       </c>
       <c r="N55" t="n">
-        <v>2.17</v>
+        <v>4.86</v>
       </c>
       <c r="O55" t="n">
         <v>-5.38</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>9.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H56" t="n">
-        <v>5601.45</v>
+        <v>5511.6</v>
       </c>
       <c r="I56" t="n">
         <v>5594.092101804614</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>-8.539999999999999</v>
+        <v>-10.01</v>
       </c>
       <c r="L56" t="n">
-        <v>8.890000000000001</v>
+        <v>10.59</v>
       </c>
       <c r="M56" t="n">
         <v>2.38</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.09</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H57" t="n">
-        <v>4320.4</v>
+        <v>4536.7</v>
       </c>
       <c r="I57" t="n">
         <v>4485.759153317119</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K57" t="n">
-        <v>21.61</v>
+        <v>17.69</v>
       </c>
       <c r="L57" t="n">
         <v>3.15</v>
@@ -3690,7 +4373,7 @@
         <v>3.13</v>
       </c>
       <c r="N57" t="n">
-        <v>3.61</v>
+        <v>5.01</v>
       </c>
       <c r="O57" t="n">
         <v>-1.6</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.22</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="H58" t="n">
-        <v>5194.5</v>
+        <v>5124</v>
       </c>
       <c r="I58" t="n">
         <v>5136.910287994803</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K58" t="n">
-        <v>14.5</v>
+        <v>12.95</v>
       </c>
       <c r="L58" t="n">
         <v>3.02</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.41</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H59" t="n">
-        <v>5341.5</v>
+        <v>5375.5</v>
       </c>
       <c r="I59" t="n">
         <v>5347.193113463481</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.24</v>
+        <v>-4.91</v>
       </c>
       <c r="L59" t="n">
         <v>5.37</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.48</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H60" t="n">
-        <v>5214</v>
+        <v>5075</v>
       </c>
       <c r="I60" t="n">
         <v>5189.784098882032</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>-3</v>
+        <v>-5.59</v>
       </c>
       <c r="L60" t="n">
-        <v>3.54</v>
+        <v>6.2</v>
       </c>
       <c r="M60" t="n">
         <v>2.8</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.09</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H61" t="n">
-        <v>5434</v>
+        <v>5471.5</v>
       </c>
       <c r="I61" t="n">
         <v>5459.477389994199</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.07</v>
+        <v>-7.81</v>
       </c>
       <c r="L61" t="n">
-        <v>8.390000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="M61" t="n">
         <v>1.92</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.81</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H62" t="n">
-        <v>5976.5</v>
+        <v>5844</v>
       </c>
       <c r="I62" t="n">
         <v>5953.817925579583</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K62" t="n">
-        <v>9.23</v>
+        <v>6.81</v>
       </c>
       <c r="L62" t="n">
         <v>1.66</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H63" t="n">
-        <v>4466.6</v>
+        <v>4628.7</v>
       </c>
       <c r="I63" t="n">
         <v>4590.888806181457</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K63" t="n">
-        <v>23.57</v>
+        <v>20.8</v>
       </c>
       <c r="L63" t="n">
         <v>7.38</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>11.79</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H64" t="n">
-        <v>4323.1</v>
+        <v>4269.6</v>
       </c>
       <c r="I64" t="n">
         <v>4277.589863174779</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.6</v>
+        <v>-7.76</v>
       </c>
       <c r="L64" t="n">
         <v>8.4</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.86</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="H65" t="n">
-        <v>3854.4</v>
+        <v>4037.2</v>
       </c>
       <c r="I65" t="n">
         <v>3927.885892632685</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K65" t="n">
-        <v>9.720000000000001</v>
+        <v>5.44</v>
       </c>
       <c r="L65" t="n">
         <v>3.15</v>
@@ -4146,7 +4925,7 @@
         <v>1.96</v>
       </c>
       <c r="N65" t="n">
-        <v>4.42</v>
+        <v>4.74</v>
       </c>
       <c r="O65" t="n">
         <v>-1.24</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>10.92</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H66" t="n">
-        <v>4374</v>
+        <v>4275</v>
       </c>
       <c r="I66" t="n">
         <v>4370.379497711263</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K66" t="n">
-        <v>8.34</v>
+        <v>5.89</v>
       </c>
       <c r="L66" t="n">
         <v>3.4</v>
       </c>
       <c r="M66" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="N66" t="n">
         <v>2.93</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.82</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H67" t="n">
-        <v>4235</v>
+        <v>4390</v>
       </c>
       <c r="I67" t="n">
         <v>4348.002853694849</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.69</v>
       </c>
       <c r="L67" t="n">
         <v>6.87</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4320,6 +5135,14 @@
       <c r="Q68" t="n">
         <v>8</v>
       </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8666,7 +9489,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="6">
@@ -8676,7 +9499,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="7">
@@ -8686,7 +9509,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8">
@@ -8696,7 +9519,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8706,7 +9529,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.8</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="10">
@@ -8716,7 +9539,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113.5</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="11">
@@ -8756,7 +9579,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.46</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="15">
@@ -8766,7 +9589,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.07</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="16">
@@ -8776,7 +9599,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.84</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
@@ -8786,7 +9609,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>115.41</v>
+        <v>107.31</v>
       </c>
     </row>
     <row r="18">
@@ -8796,7 +9619,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="19">
@@ -8806,7 +9629,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="20">
@@ -8816,7 +9639,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -8826,7 +9649,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.55</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="22">
@@ -8836,7 +9659,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -8846,7 +9669,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -8856,7 +9679,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="25">
@@ -8866,7 +9689,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.8</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -8876,7 +9699,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.88</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="27">
@@ -8886,7 +9709,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.97</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="28">
@@ -8896,7 +9719,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
